--- a/demo_output/figure_00_Aktieafkast — S&P 500, Euro Stoxx 50, Nikkei .xlsx
+++ b/demo_output/figure_00_Aktieafkast — S&P 500, Euro Stoxx 50, Nikkei .xlsx
@@ -37842,7 +37842,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>49.41422653198242</v>
+        <v>49.41421890258789</v>
       </c>
     </row>
     <row r="3">
@@ -37852,7 +37852,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>49.54828262329102</v>
+        <v>49.54827880859375</v>
       </c>
     </row>
     <row r="4">
@@ -37862,7 +37862,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>49.20866394042969</v>
+        <v>49.20866775512695</v>
       </c>
     </row>
     <row r="5">
@@ -37882,7 +37882,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>48.80648803710938</v>
+        <v>48.80648422241211</v>
       </c>
     </row>
     <row r="7">
@@ -37892,7 +37892,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>48.46686935424805</v>
+        <v>48.46687316894531</v>
       </c>
     </row>
     <row r="8">
@@ -37902,7 +37902,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>48.67243194580078</v>
+        <v>48.67242813110352</v>
       </c>
     </row>
     <row r="9">
@@ -37922,7 +37922,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>48.74393081665039</v>
+        <v>48.74393463134766</v>
       </c>
     </row>
     <row r="11">
@@ -37952,7 +37952,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>49.64659881591797</v>
+        <v>49.64659118652344</v>
       </c>
     </row>
     <row r="14">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>49.61084365844727</v>
+        <v>49.61084747314453</v>
       </c>
     </row>
     <row r="15">
@@ -37982,7 +37982,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>49.01204681396484</v>
+        <v>49.01204299926758</v>
       </c>
     </row>
     <row r="17">
@@ -37992,7 +37992,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>48.95841598510742</v>
+        <v>48.95841979980469</v>
       </c>
     </row>
     <row r="18">
@@ -38012,7 +38012,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>48.04681015014648</v>
+        <v>48.04682159423828</v>
       </c>
     </row>
     <row r="20">
@@ -38032,7 +38032,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>47.85913467407227</v>
+        <v>47.859130859375</v>
       </c>
     </row>
     <row r="22">
@@ -38042,7 +38042,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>47.9038200378418</v>
+        <v>47.90382385253906</v>
       </c>
     </row>
     <row r="23">
@@ -38052,7 +38052,7 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>47.94850921630859</v>
+        <v>47.94850540161133</v>
       </c>
     </row>
     <row r="24">
@@ -38072,7 +38072,7 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>48.27024841308594</v>
+        <v>48.2702522277832</v>
       </c>
     </row>
     <row r="26">
@@ -38082,7 +38082,7 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>47.89488220214844</v>
+        <v>47.8948860168457</v>
       </c>
     </row>
     <row r="27">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>47.09052658081055</v>
+        <v>47.09053039550781</v>
       </c>
     </row>
     <row r="28">
@@ -38102,7 +38102,7 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>47.24246215820312</v>
+        <v>47.24246597290039</v>
       </c>
     </row>
     <row r="29">
@@ -38112,7 +38112,7 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>47.54633331298828</v>
+        <v>47.54632949829102</v>
       </c>
     </row>
     <row r="30">
@@ -38122,7 +38122,7 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>47.63570404052734</v>
+        <v>47.63570785522461</v>
       </c>
     </row>
     <row r="31">
@@ -38132,7 +38132,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46.92966079711914</v>
+        <v>46.92966461181641</v>
       </c>
     </row>
     <row r="32">
@@ -38152,7 +38152,7 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45.10646057128906</v>
+        <v>45.1064567565918</v>
       </c>
     </row>
     <row r="34">
@@ -38162,7 +38162,7 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46.33086395263672</v>
+        <v>46.33086013793945</v>
       </c>
     </row>
     <row r="35">
@@ -38182,7 +38182,7 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46.11636352539062</v>
+        <v>46.11636734008789</v>
       </c>
     </row>
     <row r="37">
@@ -38192,7 +38192,7 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46.44704055786133</v>
+        <v>46.44704437255859</v>
       </c>
     </row>
     <row r="38">
@@ -38202,7 +38202,7 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46.6436653137207</v>
+        <v>46.64366149902344</v>
       </c>
     </row>
     <row r="39">
@@ -38212,7 +38212,7 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46.88496780395508</v>
+        <v>46.88497543334961</v>
       </c>
     </row>
     <row r="40">
@@ -38222,7 +38222,7 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46.81347274780273</v>
+        <v>46.81348037719727</v>
       </c>
     </row>
     <row r="41">
@@ -38232,7 +38232,7 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46.42024230957031</v>
+        <v>46.42023468017578</v>
       </c>
     </row>
     <row r="42">
@@ -38242,7 +38242,7 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46.57217025756836</v>
+        <v>46.57217788696289</v>
       </c>
     </row>
     <row r="43">
@@ -38252,7 +38252,7 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46.63473129272461</v>
+        <v>46.63472747802734</v>
       </c>
     </row>
     <row r="44">
@@ -38272,7 +38272,7 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46.34873962402344</v>
+        <v>46.34873580932617</v>
       </c>
     </row>
     <row r="46">
@@ -38302,7 +38302,7 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>44.97239303588867</v>
+        <v>44.97239685058594</v>
       </c>
     </row>
     <row r="49">
@@ -38342,7 +38342,7 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>44.90983581542969</v>
+        <v>44.90983200073242</v>
       </c>
     </row>
     <row r="53">
@@ -38352,7 +38352,7 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45.92867660522461</v>
+        <v>45.92868423461914</v>
       </c>
     </row>
     <row r="54">
@@ -38372,7 +38372,7 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45.54438400268555</v>
+        <v>45.54438018798828</v>
       </c>
     </row>
     <row r="56">
@@ -38382,7 +38382,7 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46.10742568969727</v>
+        <v>46.1074333190918</v>
       </c>
     </row>
     <row r="57">
@@ -38392,7 +38392,7 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46.20573806762695</v>
+        <v>46.20574569702148</v>
       </c>
     </row>
     <row r="58">
@@ -38422,7 +38422,7 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>47.22459030151367</v>
+        <v>47.22459411621094</v>
       </c>
     </row>
     <row r="61">
@@ -38432,7 +38432,7 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>47.47483444213867</v>
+        <v>47.47483062744141</v>
       </c>
     </row>
     <row r="62">
@@ -38462,7 +38462,7 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46.96540832519531</v>
+        <v>46.96541213989258</v>
       </c>
     </row>
     <row r="65">
@@ -38472,7 +38472,7 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46.91178131103516</v>
+        <v>46.91178512573242</v>
       </c>
     </row>
     <row r="66">
@@ -38482,7 +38482,7 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>47.03691101074219</v>
+        <v>47.03690719604492</v>
       </c>
     </row>
     <row r="67">
@@ -38492,7 +38492,7 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46.6436653137207</v>
+        <v>46.64366149902344</v>
       </c>
     </row>
     <row r="68">
@@ -38502,7 +38502,7 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46.63473129272461</v>
+        <v>46.63472747802734</v>
       </c>
     </row>
     <row r="69">
@@ -38512,7 +38512,7 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46.10742568969727</v>
+        <v>46.1074333190918</v>
       </c>
     </row>
     <row r="70">
@@ -38532,7 +38532,7 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>44.67746353149414</v>
+        <v>44.67746734619141</v>
       </c>
     </row>
     <row r="72">
@@ -38542,7 +38542,7 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>45.00815200805664</v>
+        <v>45.00814819335938</v>
       </c>
     </row>
     <row r="73">
@@ -38552,7 +38552,7 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>45.57119750976562</v>
+        <v>45.57118606567383</v>
       </c>
     </row>
     <row r="74">
@@ -38562,7 +38562,7 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>45.92867660522461</v>
+        <v>45.92868423461914</v>
       </c>
     </row>
     <row r="75">
@@ -38572,7 +38572,7 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>45.38351058959961</v>
+        <v>45.38350677490234</v>
       </c>
     </row>
     <row r="76">
@@ -38582,7 +38582,7 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>45.67843627929688</v>
+        <v>45.67844009399414</v>
       </c>
     </row>
     <row r="77">
@@ -38602,7 +38602,7 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>44.66852569580078</v>
+        <v>44.66852951049805</v>
       </c>
     </row>
     <row r="79">
@@ -38622,7 +38622,7 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>44.9813346862793</v>
+        <v>44.98133850097656</v>
       </c>
     </row>
     <row r="81">
@@ -38632,7 +38632,7 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>44.31996917724609</v>
+        <v>44.31997299194336</v>
       </c>
     </row>
     <row r="82">
@@ -38642,7 +38642,7 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>44.63278198242188</v>
+        <v>44.63277435302734</v>
       </c>
     </row>
     <row r="83">
@@ -38652,7 +38652,7 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>44.38253402709961</v>
+        <v>44.38253784179688</v>
       </c>
     </row>
     <row r="84">
@@ -38662,7 +38662,7 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>45.24945831298828</v>
+        <v>45.24945068359375</v>
       </c>
     </row>
     <row r="85">
@@ -38692,7 +38692,7 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>45.0975227355957</v>
+        <v>45.09751510620117</v>
       </c>
     </row>
     <row r="88">
@@ -38702,7 +38702,7 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>45.72312927246094</v>
+        <v>45.72312545776367</v>
       </c>
     </row>
     <row r="89">
@@ -38712,7 +38712,7 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>45.86612319946289</v>
+        <v>45.86611938476562</v>
       </c>
     </row>
     <row r="90">
@@ -38722,7 +38722,7 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46.42024230957031</v>
+        <v>46.42023468017578</v>
       </c>
     </row>
     <row r="91">
@@ -38732,7 +38732,7 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46.30405426025391</v>
+        <v>46.30405044555664</v>
       </c>
     </row>
     <row r="92">
@@ -38742,7 +38742,7 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46.92071914672852</v>
+        <v>46.92072296142578</v>
       </c>
     </row>
     <row r="93">
@@ -38752,7 +38752,7 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46.91178131103516</v>
+        <v>46.91178512573242</v>
       </c>
     </row>
     <row r="94">
@@ -38802,7 +38802,7 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>46.13424301147461</v>
+        <v>46.13423538208008</v>
       </c>
     </row>
     <row r="99">
@@ -38812,7 +38812,7 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>46.17892837524414</v>
+        <v>46.17892456054688</v>
       </c>
     </row>
     <row r="100">
@@ -38822,7 +38822,7 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50863647460938</v>
       </c>
     </row>
     <row r="101">
@@ -38832,7 +38832,7 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45.86612319946289</v>
+        <v>45.86611938476562</v>
       </c>
     </row>
     <row r="102">
@@ -38842,7 +38842,7 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45.45500564575195</v>
+        <v>45.45501327514648</v>
       </c>
     </row>
     <row r="103">
@@ -38852,7 +38852,7 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45.66950607299805</v>
+        <v>45.66950225830078</v>
       </c>
     </row>
     <row r="104">
@@ -38872,7 +38872,7 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50863647460938</v>
       </c>
     </row>
     <row r="106">
@@ -38882,7 +38882,7 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45.92867660522461</v>
+        <v>45.92868423461914</v>
       </c>
     </row>
     <row r="107">
@@ -38892,7 +38892,7 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45.74993515014648</v>
+        <v>45.74994277954102</v>
       </c>
     </row>
     <row r="108">
@@ -38912,7 +38912,7 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>46.34873962402344</v>
+        <v>46.34873580932617</v>
       </c>
     </row>
     <row r="110">
@@ -38922,7 +38922,7 @@
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>46.47386169433594</v>
+        <v>46.47385787963867</v>
       </c>
     </row>
     <row r="111">
@@ -38932,7 +38932,7 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>46.32192611694336</v>
+        <v>46.32192993164062</v>
       </c>
     </row>
     <row r="112">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>46.38449096679688</v>
+        <v>46.38448715209961</v>
       </c>
     </row>
     <row r="113">
@@ -38952,7 +38952,7 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>46.1431770324707</v>
+        <v>46.14318466186523</v>
       </c>
     </row>
     <row r="114">
@@ -38962,7 +38962,7 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45.58013153076172</v>
+        <v>45.58013916015625</v>
       </c>
     </row>
     <row r="115">
@@ -38972,7 +38972,7 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45.50863265991211</v>
+        <v>45.50863647460938</v>
       </c>
     </row>
     <row r="116">
@@ -38982,7 +38982,7 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45.14220809936523</v>
+        <v>45.1422004699707</v>
       </c>
     </row>
     <row r="117">
@@ -38992,7 +38992,7 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45.0975227355957</v>
+        <v>45.09751510620117</v>
       </c>
     </row>
     <row r="118">
@@ -39002,7 +39002,7 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45.03495788574219</v>
+        <v>45.03496170043945</v>
       </c>
     </row>
     <row r="119">
@@ -39022,7 +39022,7 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>43.69435882568359</v>
+        <v>43.69436645507812</v>
       </c>
     </row>
     <row r="121">
@@ -39032,7 +39032,7 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>43.64968109130859</v>
+        <v>43.64967727661133</v>
       </c>
     </row>
     <row r="122">
@@ -39042,7 +39042,7 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>43.810546875</v>
+        <v>43.81055068969727</v>
       </c>
     </row>
     <row r="123">
@@ -39052,7 +39052,7 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>44.3467903137207</v>
+        <v>44.34678268432617</v>
       </c>
     </row>
     <row r="124">
@@ -39072,7 +39072,7 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>44.06079864501953</v>
+        <v>44.060791015625</v>
       </c>
     </row>
     <row r="126">
@@ -39082,7 +39082,7 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>44.75790023803711</v>
+        <v>44.75790786743164</v>
       </c>
     </row>
     <row r="127">
@@ -39102,7 +39102,7 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>44.72214889526367</v>
+        <v>44.72215270996094</v>
       </c>
     </row>
     <row r="129">
@@ -39112,7 +39112,7 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>44.75790023803711</v>
+        <v>44.75790786743164</v>
       </c>
     </row>
     <row r="130">
@@ -39122,7 +39122,7 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>44.04808807373047</v>
+        <v>44.048095703125</v>
       </c>
     </row>
     <row r="131">
@@ -39152,7 +39152,7 @@
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>43.87585067749023</v>
+        <v>43.8758544921875</v>
       </c>
     </row>
     <row r="134">
@@ -39162,7 +39162,7 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>43.65828323364258</v>
+        <v>43.65828704833984</v>
       </c>
     </row>
     <row r="135">
@@ -39172,7 +39172,7 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>43.00558853149414</v>
+        <v>43.00558090209961</v>
       </c>
     </row>
     <row r="136">
@@ -39202,7 +39202,7 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>44.16594696044922</v>
+        <v>44.16593551635742</v>
       </c>
     </row>
     <row r="139">
@@ -39212,7 +39212,7 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>44.36537933349609</v>
+        <v>44.36537551879883</v>
       </c>
     </row>
     <row r="140">
@@ -39232,7 +39232,7 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>44.02089691162109</v>
+        <v>44.02090072631836</v>
       </c>
     </row>
     <row r="142">
@@ -39242,7 +39242,7 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>44.52519989013672</v>
+        <v>44.52519607543945</v>
       </c>
     </row>
     <row r="143">
@@ -39252,7 +39252,7 @@
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>44.3075065612793</v>
+        <v>44.30751419067383</v>
       </c>
     </row>
     <row r="144">
@@ -39282,7 +39282,7 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>43.74516677856445</v>
+        <v>43.74516296386719</v>
       </c>
     </row>
     <row r="147">
@@ -39292,7 +39292,7 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>43.94470977783203</v>
+        <v>43.94470596313477</v>
       </c>
     </row>
     <row r="148">
@@ -39332,7 +39332,7 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>46.12153244018555</v>
+        <v>46.12153625488281</v>
       </c>
     </row>
     <row r="152">
@@ -39342,7 +39342,7 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>45.46848678588867</v>
+        <v>45.46848297119141</v>
       </c>
     </row>
     <row r="153">
@@ -39352,7 +39352,7 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>45.45034408569336</v>
+        <v>45.45034790039062</v>
       </c>
     </row>
     <row r="154">
@@ -39452,7 +39452,7 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>44.29843902587891</v>
+        <v>44.29844284057617</v>
       </c>
     </row>
     <row r="164">
@@ -39462,7 +39462,7 @@
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>44.57054901123047</v>
+        <v>44.5705451965332</v>
       </c>
     </row>
     <row r="165">
@@ -39472,7 +39472,7 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>44.49798202514648</v>
+        <v>44.49798583984375</v>
       </c>
     </row>
     <row r="166">
@@ -39482,7 +39482,7 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>44.02634048461914</v>
+        <v>44.02633666992188</v>
       </c>
     </row>
     <row r="167">
@@ -39492,7 +39492,7 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>44.13517761230469</v>
+        <v>44.13517379760742</v>
       </c>
     </row>
     <row r="168">
@@ -39502,7 +39502,7 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>44.04447937011719</v>
+        <v>44.04448318481445</v>
       </c>
     </row>
     <row r="169">
@@ -39522,7 +39522,7 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>45.16917037963867</v>
+        <v>45.16917419433594</v>
       </c>
     </row>
     <row r="171">
@@ -39542,7 +39542,7 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>44.18960571289062</v>
+        <v>44.18959808349609</v>
       </c>
     </row>
     <row r="173">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>43.8812141418457</v>
+        <v>43.88121795654297</v>
       </c>
     </row>
     <row r="174">
@@ -39582,7 +39582,7 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>44.634033203125</v>
+        <v>44.63403701782227</v>
       </c>
     </row>
     <row r="177">
@@ -39592,7 +39592,7 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>44.18960571289062</v>
+        <v>44.18959808349609</v>
       </c>
     </row>
     <row r="178">
@@ -39622,7 +39622,7 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>42.16696548461914</v>
+        <v>42.16697311401367</v>
       </c>
     </row>
     <row r="181">
@@ -39642,7 +39642,7 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>42.38464736938477</v>
+        <v>42.3846435546875</v>
       </c>
     </row>
     <row r="183">
@@ -39652,7 +39652,7 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>41.82230377197266</v>
+        <v>41.82229995727539</v>
       </c>
     </row>
     <row r="184">
@@ -39662,7 +39662,7 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>41.89486312866211</v>
+        <v>41.89485931396484</v>
       </c>
     </row>
     <row r="185">
@@ -39682,7 +39682,7 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>40.47085571289062</v>
+        <v>40.47085189819336</v>
       </c>
     </row>
     <row r="187">
@@ -39692,7 +39692,7 @@
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>38.95614624023438</v>
+        <v>38.95614242553711</v>
       </c>
     </row>
     <row r="188">
@@ -39702,7 +39702,7 @@
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>39.08312225341797</v>
+        <v>39.08312606811523</v>
       </c>
     </row>
     <row r="189">
@@ -39712,7 +39712,7 @@
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>40.18967437744141</v>
+        <v>40.1896858215332</v>
       </c>
     </row>
     <row r="190">
@@ -39722,7 +39722,7 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>39.43685913085938</v>
+        <v>39.43686294555664</v>
       </c>
     </row>
     <row r="191">
@@ -39732,7 +39732,7 @@
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>38.61148071289062</v>
+        <v>38.61148452758789</v>
       </c>
     </row>
     <row r="192">
@@ -39742,7 +39742,7 @@
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>37.67725372314453</v>
+        <v>37.67726135253906</v>
       </c>
     </row>
     <row r="193">
@@ -39772,7 +39772,7 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>40.56155395507812</v>
+        <v>40.56155776977539</v>
       </c>
     </row>
     <row r="196">
@@ -39822,7 +39822,7 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>41.18739318847656</v>
+        <v>41.1873893737793</v>
       </c>
     </row>
     <row r="201">
@@ -39832,7 +39832,7 @@
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>40.86086654663086</v>
+        <v>40.86086273193359</v>
       </c>
     </row>
     <row r="202">
@@ -39842,7 +39842,7 @@
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>40.99691390991211</v>
+        <v>40.99691772460938</v>
       </c>
     </row>
     <row r="203">
@@ -39852,7 +39852,7 @@
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>41.69532012939453</v>
+        <v>41.6953239440918</v>
       </c>
     </row>
     <row r="204">
@@ -39862,7 +39862,7 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>41.57740783691406</v>
+        <v>41.5774040222168</v>
       </c>
     </row>
     <row r="205">
@@ -39872,7 +39872,7 @@
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>40.95156860351562</v>
+        <v>40.95157241821289</v>
       </c>
     </row>
     <row r="206">
@@ -39882,7 +39882,7 @@
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>41.63182830810547</v>
+        <v>41.63183212280273</v>
       </c>
     </row>
     <row r="207">
@@ -39892,7 +39892,7 @@
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>42.36650466918945</v>
+        <v>42.36650848388672</v>
       </c>
     </row>
     <row r="208">
@@ -39912,7 +39912,7 @@
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>41.04226684570312</v>
+        <v>41.04227447509766</v>
       </c>
     </row>
     <row r="210">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>40.71575164794922</v>
+        <v>40.71574020385742</v>
       </c>
     </row>
     <row r="211">
@@ -39932,7 +39932,7 @@
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>40.75202178955078</v>
+        <v>40.75202560424805</v>
       </c>
     </row>
     <row r="212">
@@ -39942,7 +39942,7 @@
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>40.24410247802734</v>
+        <v>40.24410629272461</v>
       </c>
     </row>
     <row r="213">
@@ -39952,7 +39952,7 @@
         </is>
       </c>
       <c r="B213" s="2" t="n">
-        <v>40.11712265014648</v>
+        <v>40.11711883544922</v>
       </c>
     </row>
     <row r="214">
@@ -39962,7 +39962,7 @@
         </is>
       </c>
       <c r="B214" s="2" t="n">
-        <v>40.64319229125977</v>
+        <v>40.6431884765625</v>
       </c>
     </row>
     <row r="215">
@@ -39972,7 +39972,7 @@
         </is>
       </c>
       <c r="B215" s="2" t="n">
-        <v>40.11712265014648</v>
+        <v>40.11711883544922</v>
       </c>
     </row>
     <row r="216">
@@ -39992,7 +39992,7 @@
         </is>
       </c>
       <c r="B217" s="2" t="n">
-        <v>39.78152084350586</v>
+        <v>39.78152465820312</v>
       </c>
     </row>
     <row r="218">
@@ -40012,7 +40012,7 @@
         </is>
       </c>
       <c r="B219" s="2" t="n">
-        <v>38.78380584716797</v>
+        <v>38.7838134765625</v>
       </c>
     </row>
     <row r="220">
@@ -40022,7 +40022,7 @@
         </is>
       </c>
       <c r="B220" s="2" t="n">
-        <v>38.43915176391602</v>
+        <v>38.43915557861328</v>
       </c>
     </row>
     <row r="221">
@@ -40032,7 +40032,7 @@
         </is>
       </c>
       <c r="B221" s="2" t="n">
-        <v>38.1579704284668</v>
+        <v>38.15797424316406</v>
       </c>
     </row>
     <row r="222">
@@ -40042,7 +40042,7 @@
         </is>
       </c>
       <c r="B222" s="2" t="n">
-        <v>37.32352447509766</v>
+        <v>37.32352066040039</v>
       </c>
     </row>
     <row r="223">
@@ -40052,7 +40052,7 @@
         </is>
       </c>
       <c r="B223" s="2" t="n">
-        <v>37.75889205932617</v>
+        <v>37.75888824462891</v>
       </c>
     </row>
     <row r="224">
@@ -40062,7 +40062,7 @@
         </is>
       </c>
       <c r="B224" s="2" t="n">
-        <v>38.3030891418457</v>
+        <v>38.3031005859375</v>
       </c>
     </row>
     <row r="225">
@@ -40072,7 +40072,7 @@
         </is>
       </c>
       <c r="B225" s="2" t="n">
-        <v>38.43915176391602</v>
+        <v>38.43915557861328</v>
       </c>
     </row>
     <row r="226">
@@ -40082,7 +40082,7 @@
         </is>
       </c>
       <c r="B226" s="2" t="n">
-        <v>38.38473129272461</v>
+        <v>38.38472366333008</v>
       </c>
     </row>
     <row r="227">
@@ -40092,7 +40092,7 @@
         </is>
       </c>
       <c r="B227" s="2" t="n">
-        <v>38.66589736938477</v>
+        <v>38.6659049987793</v>
       </c>
     </row>
     <row r="228">
@@ -40102,7 +40102,7 @@
         </is>
       </c>
       <c r="B228" s="2" t="n">
-        <v>39.08312225341797</v>
+        <v>39.08312606811523</v>
       </c>
     </row>
     <row r="229">
@@ -40112,7 +40112,7 @@
         </is>
       </c>
       <c r="B229" s="2" t="n">
-        <v>37.64097595214844</v>
+        <v>37.6409797668457</v>
       </c>
     </row>
     <row r="230">
@@ -40122,7 +40122,7 @@
         </is>
       </c>
       <c r="B230" s="2" t="n">
-        <v>37.12398529052734</v>
+        <v>37.12397766113281</v>
       </c>
     </row>
     <row r="231">
@@ -40142,7 +40142,7 @@
         </is>
       </c>
       <c r="B232" s="2" t="n">
-        <v>36.22604370117188</v>
+        <v>36.22603988647461</v>
       </c>
     </row>
     <row r="233">
@@ -40152,7 +40152,7 @@
         </is>
       </c>
       <c r="B233" s="2" t="n">
-        <v>35.97207260131836</v>
+        <v>35.97207641601562</v>
       </c>
     </row>
     <row r="234">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="B234" s="2" t="n">
-        <v>35.73625183105469</v>
+        <v>35.73625564575195</v>
       </c>
     </row>
     <row r="235">
@@ -40172,7 +40172,7 @@
         </is>
       </c>
       <c r="B235" s="2" t="n">
-        <v>36.72489547729492</v>
+        <v>36.72489929199219</v>
       </c>
     </row>
     <row r="236">
@@ -40182,7 +40182,7 @@
         </is>
       </c>
       <c r="B236" s="2" t="n">
-        <v>36.57977676391602</v>
+        <v>36.57977294921875</v>
       </c>
     </row>
     <row r="237">
@@ -40192,7 +40192,7 @@
         </is>
       </c>
       <c r="B237" s="2" t="n">
-        <v>37.47772216796875</v>
+        <v>37.47771835327148</v>
       </c>
     </row>
     <row r="238">
@@ -40202,7 +40202,7 @@
         </is>
       </c>
       <c r="B238" s="2" t="n">
-        <v>36.57977676391602</v>
+        <v>36.57977294921875</v>
       </c>
     </row>
     <row r="239">
@@ -40212,7 +40212,7 @@
         </is>
       </c>
       <c r="B239" s="2" t="n">
-        <v>37.16026306152344</v>
+        <v>37.16027069091797</v>
       </c>
     </row>
     <row r="240">
@@ -40222,7 +40222,7 @@
         </is>
       </c>
       <c r="B240" s="2" t="n">
-        <v>37.31444549560547</v>
+        <v>37.314453125</v>
       </c>
     </row>
     <row r="241">
@@ -40252,7 +40252,7 @@
         </is>
       </c>
       <c r="B243" s="2" t="n">
-        <v>37.12398529052734</v>
+        <v>37.12397766113281</v>
       </c>
     </row>
     <row r="244">
@@ -40272,7 +40272,7 @@
         </is>
       </c>
       <c r="B245" s="2" t="n">
-        <v>38.13983535766602</v>
+        <v>38.13983154296875</v>
       </c>
     </row>
     <row r="246">
@@ -40282,7 +40282,7 @@
         </is>
       </c>
       <c r="B246" s="2" t="n">
-        <v>38.67497253417969</v>
+        <v>38.67496871948242</v>
       </c>
     </row>
     <row r="247">
@@ -40292,7 +40292,7 @@
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>38.40286254882812</v>
+        <v>38.40287017822266</v>
       </c>
     </row>
     <row r="248">
@@ -40302,7 +40302,7 @@
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>39.06498336791992</v>
+        <v>39.06498718261719</v>
       </c>
     </row>
     <row r="249">
@@ -40322,7 +40322,7 @@
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>38.6386833190918</v>
+        <v>38.63869476318359</v>
       </c>
     </row>
     <row r="251">
@@ -40342,7 +40342,7 @@
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>38.96521759033203</v>
+        <v>38.96521377563477</v>
       </c>
     </row>
     <row r="253">
@@ -40352,7 +40352,7 @@
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>38.04318237304688</v>
+        <v>38.04317092895508</v>
       </c>
     </row>
     <row r="254">
@@ -40372,7 +40372,7 @@
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>36.30520629882812</v>
+        <v>36.30521011352539</v>
       </c>
     </row>
     <row r="256">
@@ -40382,7 +40382,7 @@
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>36.80830764770508</v>
+        <v>36.80831146240234</v>
       </c>
     </row>
     <row r="257">
@@ -40392,7 +40392,7 @@
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>37.29310989379883</v>
+        <v>37.29310607910156</v>
       </c>
     </row>
     <row r="258">
@@ -40412,7 +40412,7 @@
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>36.28691482543945</v>
+        <v>36.28691101074219</v>
       </c>
     </row>
     <row r="260">
@@ -40422,7 +40422,7 @@
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>36.87233734130859</v>
+        <v>36.87234115600586</v>
       </c>
     </row>
     <row r="261">
@@ -40452,7 +40452,7 @@
         </is>
       </c>
       <c r="B263" s="2" t="n">
-        <v>37.18334197998047</v>
+        <v>37.18334579467773</v>
       </c>
     </row>
     <row r="264">
@@ -40472,7 +40472,7 @@
         </is>
       </c>
       <c r="B265" s="2" t="n">
-        <v>37.00039672851562</v>
+        <v>37.00040054321289</v>
       </c>
     </row>
     <row r="266">
@@ -40492,7 +40492,7 @@
         </is>
       </c>
       <c r="B267" s="2" t="n">
-        <v>36.68024063110352</v>
+        <v>36.68024444580078</v>
       </c>
     </row>
     <row r="268">
@@ -40512,7 +40512,7 @@
         </is>
       </c>
       <c r="B269" s="2" t="n">
-        <v>36.16800689697266</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="270">
@@ -40522,7 +40522,7 @@
         </is>
       </c>
       <c r="B270" s="2" t="n">
-        <v>35.94846725463867</v>
+        <v>35.94847106933594</v>
       </c>
     </row>
     <row r="271">
@@ -40532,7 +40532,7 @@
         </is>
       </c>
       <c r="B271" s="2" t="n">
-        <v>36.67109680175781</v>
+        <v>36.67109298706055</v>
       </c>
     </row>
     <row r="272">
@@ -40542,7 +40542,7 @@
         </is>
       </c>
       <c r="B272" s="2" t="n">
-        <v>36.67109680175781</v>
+        <v>36.67109298706055</v>
       </c>
     </row>
     <row r="273">
@@ -40572,7 +40572,7 @@
         </is>
       </c>
       <c r="B275" s="2" t="n">
-        <v>35.47281646728516</v>
+        <v>35.47281265258789</v>
       </c>
     </row>
     <row r="276">
@@ -40592,7 +40592,7 @@
         </is>
       </c>
       <c r="B277" s="2" t="n">
-        <v>35.33560943603516</v>
+        <v>35.33561325073242</v>
       </c>
     </row>
     <row r="278">
@@ -40612,7 +40612,7 @@
         </is>
       </c>
       <c r="B279" s="2" t="n">
-        <v>36.16800689697266</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="280">
@@ -40632,7 +40632,7 @@
         </is>
       </c>
       <c r="B281" s="2" t="n">
-        <v>36.42411804199219</v>
+        <v>36.42412185668945</v>
       </c>
     </row>
     <row r="282">
@@ -40642,7 +40642,7 @@
         </is>
       </c>
       <c r="B282" s="2" t="n">
-        <v>36.0582389831543</v>
+        <v>36.0582275390625</v>
       </c>
     </row>
     <row r="283">
@@ -40662,7 +40662,7 @@
         </is>
       </c>
       <c r="B284" s="2" t="n">
-        <v>35.90273666381836</v>
+        <v>35.90272903442383</v>
       </c>
     </row>
     <row r="285">
@@ -40672,7 +40672,7 @@
         </is>
       </c>
       <c r="B285" s="2" t="n">
-        <v>36.57048034667969</v>
+        <v>36.57047653198242</v>
       </c>
     </row>
     <row r="286">
@@ -40682,7 +40682,7 @@
         </is>
       </c>
       <c r="B286" s="2" t="n">
-        <v>36.72597885131836</v>
+        <v>36.72598266601562</v>
       </c>
     </row>
     <row r="287">
@@ -40702,7 +40702,7 @@
         </is>
       </c>
       <c r="B288" s="2" t="n">
-        <v>36.24118041992188</v>
+        <v>36.24117279052734</v>
       </c>
     </row>
     <row r="289">
@@ -40712,7 +40712,7 @@
         </is>
       </c>
       <c r="B289" s="2" t="n">
-        <v>36.0673828125</v>
+        <v>36.06739044189453</v>
       </c>
     </row>
     <row r="290">
@@ -40732,7 +40732,7 @@
         </is>
       </c>
       <c r="B291" s="2" t="n">
-        <v>36.60706329345703</v>
+        <v>36.6070671081543</v>
       </c>
     </row>
     <row r="292">
@@ -40742,7 +40742,7 @@
         </is>
       </c>
       <c r="B292" s="2" t="n">
-        <v>36.64365768432617</v>
+        <v>36.64366149902344</v>
       </c>
     </row>
     <row r="293">
@@ -40752,7 +40752,7 @@
         </is>
       </c>
       <c r="B293" s="2" t="n">
-        <v>36.68939208984375</v>
+        <v>36.68939590454102</v>
       </c>
     </row>
     <row r="294">
@@ -40782,7 +40782,7 @@
         </is>
       </c>
       <c r="B296" s="2" t="n">
-        <v>37.1558952331543</v>
+        <v>37.15589904785156</v>
       </c>
     </row>
     <row r="297">
@@ -40812,7 +40812,7 @@
         </is>
       </c>
       <c r="B299" s="2" t="n">
-        <v>37.36628723144531</v>
+        <v>37.36629104614258</v>
       </c>
     </row>
     <row r="300">
@@ -40822,7 +40822,7 @@
         </is>
       </c>
       <c r="B300" s="2" t="n">
-        <v>37.21077728271484</v>
+        <v>37.21078872680664</v>
       </c>
     </row>
     <row r="301">
@@ -40832,7 +40832,7 @@
         </is>
       </c>
       <c r="B301" s="2" t="n">
-        <v>37.00039672851562</v>
+        <v>37.00040054321289</v>
       </c>
     </row>
     <row r="302">
@@ -40842,7 +40842,7 @@
         </is>
       </c>
       <c r="B302" s="2" t="n">
-        <v>36.4973030090332</v>
+        <v>36.49730682373047</v>
       </c>
     </row>
     <row r="303">
@@ -40852,7 +40852,7 @@
         </is>
       </c>
       <c r="B303" s="2" t="n">
-        <v>36.17714691162109</v>
+        <v>36.17715072631836</v>
       </c>
     </row>
     <row r="304">
@@ -40862,7 +40862,7 @@
         </is>
       </c>
       <c r="B304" s="2" t="n">
-        <v>36.36923599243164</v>
+        <v>36.36923980712891</v>
       </c>
     </row>
     <row r="305">
@@ -40872,7 +40872,7 @@
         </is>
       </c>
       <c r="B305" s="2" t="n">
-        <v>36.3600959777832</v>
+        <v>36.36009216308594</v>
       </c>
     </row>
     <row r="306">
@@ -40882,7 +40882,7 @@
         </is>
       </c>
       <c r="B306" s="2" t="n">
-        <v>37.14675903320312</v>
+        <v>37.14674758911133</v>
       </c>
     </row>
     <row r="307">
@@ -40892,7 +40892,7 @@
         </is>
       </c>
       <c r="B307" s="2" t="n">
-        <v>36.59791946411133</v>
+        <v>36.59791564941406</v>
       </c>
     </row>
     <row r="308">
@@ -40902,7 +40902,7 @@
         </is>
       </c>
       <c r="B308" s="2" t="n">
-        <v>36.36923599243164</v>
+        <v>36.36923980712891</v>
       </c>
     </row>
     <row r="309">
@@ -40922,7 +40922,7 @@
         </is>
       </c>
       <c r="B310" s="2" t="n">
-        <v>36.0673828125</v>
+        <v>36.06739044189453</v>
       </c>
     </row>
     <row r="311">
@@ -40952,7 +40952,7 @@
         </is>
       </c>
       <c r="B313" s="2" t="n">
-        <v>35.03375625610352</v>
+        <v>35.03374862670898</v>
       </c>
     </row>
     <row r="314">
@@ -40992,7 +40992,7 @@
         </is>
       </c>
       <c r="B317" s="2" t="n">
-        <v>36.20459365844727</v>
+        <v>36.20458984375</v>
       </c>
     </row>
     <row r="318">
@@ -41002,7 +41002,7 @@
         </is>
       </c>
       <c r="B318" s="2" t="n">
-        <v>35.08863830566406</v>
+        <v>35.08863067626953</v>
       </c>
     </row>
     <row r="319">
@@ -41012,7 +41012,7 @@
         </is>
       </c>
       <c r="B319" s="2" t="n">
-        <v>35.26243209838867</v>
+        <v>35.26242828369141</v>
       </c>
     </row>
     <row r="320">
@@ -41022,7 +41022,7 @@
         </is>
       </c>
       <c r="B320" s="2" t="n">
-        <v>34.88739776611328</v>
+        <v>34.88739395141602</v>
       </c>
     </row>
     <row r="321">
@@ -41052,7 +41052,7 @@
         </is>
       </c>
       <c r="B323" s="2" t="n">
-        <v>34.48492431640625</v>
+        <v>34.48491668701172</v>
       </c>
     </row>
     <row r="324">
@@ -41062,7 +41062,7 @@
         </is>
       </c>
       <c r="B324" s="2" t="n">
-        <v>33.90864562988281</v>
+        <v>33.90864181518555</v>
       </c>
     </row>
     <row r="325">
@@ -41082,7 +41082,7 @@
         </is>
       </c>
       <c r="B326" s="2" t="n">
-        <v>32.91160202026367</v>
+        <v>32.91159820556641</v>
       </c>
     </row>
     <row r="327">
@@ -41102,7 +41102,7 @@
         </is>
       </c>
       <c r="B328" s="2" t="n">
-        <v>32.47253799438477</v>
+        <v>32.4725341796875</v>
       </c>
     </row>
     <row r="329">
@@ -41122,7 +41122,7 @@
         </is>
       </c>
       <c r="B330" s="2" t="n">
-        <v>32.02431869506836</v>
+        <v>32.02432632446289</v>
       </c>
     </row>
     <row r="331">
@@ -41132,7 +41132,7 @@
         </is>
       </c>
       <c r="B331" s="2" t="n">
-        <v>31.90540313720703</v>
+        <v>31.90541458129883</v>
       </c>
     </row>
     <row r="332">
@@ -41162,7 +41162,7 @@
         </is>
       </c>
       <c r="B334" s="2" t="n">
-        <v>33.50617218017578</v>
+        <v>33.50617599487305</v>
       </c>
     </row>
     <row r="335">
@@ -41172,7 +41172,7 @@
         </is>
       </c>
       <c r="B335" s="2" t="n">
-        <v>33.304931640625</v>
+        <v>33.30493545532227</v>
       </c>
     </row>
     <row r="336">
@@ -41192,7 +41192,7 @@
         </is>
       </c>
       <c r="B337" s="2" t="n">
-        <v>32.15238189697266</v>
+        <v>32.15237808227539</v>
       </c>
     </row>
     <row r="338">
@@ -41212,7 +41212,7 @@
         </is>
       </c>
       <c r="B339" s="2" t="n">
-        <v>31.67673110961914</v>
+        <v>31.67673492431641</v>
       </c>
     </row>
     <row r="340">
@@ -41222,7 +41222,7 @@
         </is>
       </c>
       <c r="B340" s="2" t="n">
-        <v>31.76820373535156</v>
+        <v>31.7681999206543</v>
       </c>
     </row>
     <row r="341">
@@ -41242,7 +41242,7 @@
         </is>
       </c>
       <c r="B342" s="2" t="n">
-        <v>32.15238189697266</v>
+        <v>32.15237808227539</v>
       </c>
     </row>
     <row r="343">
@@ -41262,7 +41262,7 @@
         </is>
       </c>
       <c r="B344" s="2" t="n">
-        <v>31.57611083984375</v>
+        <v>31.57610893249512</v>
       </c>
     </row>
     <row r="345">
@@ -41272,7 +41272,7 @@
         </is>
       </c>
       <c r="B345" s="2" t="n">
-        <v>31.77735137939453</v>
+        <v>31.7773494720459</v>
       </c>
     </row>
     <row r="346">
@@ -41292,7 +41292,7 @@
         </is>
       </c>
       <c r="B347" s="2" t="n">
-        <v>31.03642463684082</v>
+        <v>31.03642845153809</v>
       </c>
     </row>
     <row r="348">
@@ -41322,7 +41322,7 @@
         </is>
       </c>
       <c r="B350" s="2" t="n">
-        <v>31.55781555175781</v>
+        <v>31.55781936645508</v>
       </c>
     </row>
     <row r="351">
@@ -41342,7 +41342,7 @@
         </is>
       </c>
       <c r="B352" s="2" t="n">
-        <v>31.27425003051758</v>
+        <v>31.27425384521484</v>
       </c>
     </row>
     <row r="353">
@@ -41352,7 +41352,7 @@
         </is>
       </c>
       <c r="B353" s="2" t="n">
-        <v>31.85052680969238</v>
+        <v>31.85053062438965</v>
       </c>
     </row>
     <row r="354">
@@ -41372,7 +41372,7 @@
         </is>
       </c>
       <c r="B355" s="2" t="n">
-        <v>31.76820373535156</v>
+        <v>31.7681999206543</v>
       </c>
     </row>
     <row r="356">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="B356" s="2" t="n">
-        <v>33.11283874511719</v>
+        <v>33.11284255981445</v>
       </c>
     </row>
     <row r="357">
@@ -41392,7 +41392,7 @@
         </is>
       </c>
       <c r="B357" s="2" t="n">
-        <v>33.13113021850586</v>
+        <v>33.13113403320312</v>
       </c>
     </row>
     <row r="358">
@@ -41402,7 +41402,7 @@
         </is>
       </c>
       <c r="B358" s="2" t="n">
-        <v>33.36896133422852</v>
+        <v>33.36895751953125</v>
       </c>
     </row>
     <row r="359">
@@ -41412,7 +41412,7 @@
         </is>
       </c>
       <c r="B359" s="2" t="n">
-        <v>32.79268646240234</v>
+        <v>32.79268264770508</v>
       </c>
     </row>
     <row r="360">
@@ -41422,7 +41422,7 @@
         </is>
       </c>
       <c r="B360" s="2" t="n">
-        <v>33.98182678222656</v>
+        <v>33.98181915283203</v>
       </c>
     </row>
     <row r="361">
@@ -41442,7 +41442,7 @@
         </is>
       </c>
       <c r="B362" s="2" t="n">
-        <v>34.69530868530273</v>
+        <v>34.69530487060547</v>
       </c>
     </row>
     <row r="363">
@@ -41452,7 +41452,7 @@
         </is>
       </c>
       <c r="B363" s="2" t="n">
-        <v>35.49110794067383</v>
+        <v>35.49111175537109</v>
       </c>
     </row>
     <row r="364">
@@ -41462,7 +41462,7 @@
         </is>
       </c>
       <c r="B364" s="2" t="n">
-        <v>34.92398071289062</v>
+        <v>34.92398452758789</v>
       </c>
     </row>
     <row r="365">
@@ -41522,7 +41522,7 @@
         </is>
       </c>
       <c r="B370" s="2" t="n">
-        <v>34.54895401000977</v>
+        <v>34.5489501953125</v>
       </c>
     </row>
     <row r="371">
@@ -41532,7 +41532,7 @@
         </is>
       </c>
       <c r="B371" s="2" t="n">
-        <v>34.39344787597656</v>
+        <v>34.3934440612793</v>
       </c>
     </row>
     <row r="372">
@@ -41542,7 +41542,7 @@
         </is>
       </c>
       <c r="B372" s="2" t="n">
-        <v>35.13436889648438</v>
+        <v>35.13436508178711</v>
       </c>
     </row>
     <row r="373">
@@ -41572,7 +41572,7 @@
         </is>
       </c>
       <c r="B375" s="2" t="n">
-        <v>36.16800689697266</v>
+        <v>36.16800308227539</v>
       </c>
     </row>
     <row r="376">
@@ -41582,7 +41582,7 @@
         </is>
       </c>
       <c r="B376" s="2" t="n">
-        <v>35.75638580322266</v>
+        <v>35.75638198852539</v>
       </c>
     </row>
     <row r="377">
@@ -41592,7 +41592,7 @@
         </is>
       </c>
       <c r="B377" s="2" t="n">
-        <v>35.71064376831055</v>
+        <v>35.71063995361328</v>
       </c>
     </row>
     <row r="378">
@@ -41612,7 +41612,7 @@
         </is>
       </c>
       <c r="B379" s="2" t="n">
-        <v>35.93017196655273</v>
+        <v>35.93016815185547</v>
       </c>
     </row>
     <row r="380">
@@ -41652,7 +41652,7 @@
         </is>
       </c>
       <c r="B383" s="2" t="n">
-        <v>35.85560989379883</v>
+        <v>35.8556022644043</v>
       </c>
     </row>
     <row r="384">
@@ -41682,7 +41682,7 @@
         </is>
       </c>
       <c r="B386" s="2" t="n">
-        <v>35.15911483764648</v>
+        <v>35.15911865234375</v>
       </c>
     </row>
     <row r="387">
@@ -41702,7 +41702,7 @@
         </is>
       </c>
       <c r="B388" s="2" t="n">
-        <v>35.46556854248047</v>
+        <v>35.4655647277832</v>
       </c>
     </row>
     <row r="389">
@@ -41732,7 +41732,7 @@
         </is>
       </c>
       <c r="B391" s="2" t="n">
-        <v>35.62344741821289</v>
+        <v>35.62343978881836</v>
       </c>
     </row>
     <row r="392">
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="B393" s="2" t="n">
-        <v>35.68844985961914</v>
+        <v>35.68845367431641</v>
       </c>
     </row>
     <row r="394">
@@ -41782,7 +41782,7 @@
         </is>
       </c>
       <c r="B396" s="2" t="n">
-        <v>36.56139373779297</v>
+        <v>36.5613899230957</v>
       </c>
     </row>
     <row r="397">
@@ -41792,7 +41792,7 @@
         </is>
       </c>
       <c r="B397" s="2" t="n">
-        <v>36.449951171875</v>
+        <v>36.44994735717773</v>
       </c>
     </row>
     <row r="398">
@@ -41802,7 +41802,7 @@
         </is>
       </c>
       <c r="B398" s="2" t="n">
-        <v>37.21145248413086</v>
+        <v>37.21145629882812</v>
       </c>
     </row>
     <row r="399">
@@ -41812,7 +41812,7 @@
         </is>
       </c>
       <c r="B399" s="2" t="n">
-        <v>37.49005508422852</v>
+        <v>37.49005126953125</v>
       </c>
     </row>
     <row r="400">
@@ -41832,7 +41832,7 @@
         </is>
       </c>
       <c r="B401" s="2" t="n">
-        <v>37.917236328125</v>
+        <v>37.91723251342773</v>
       </c>
     </row>
     <row r="402">
@@ -41862,7 +41862,7 @@
         </is>
       </c>
       <c r="B404" s="2" t="n">
-        <v>38.14011764526367</v>
+        <v>38.14011383056641</v>
       </c>
     </row>
     <row r="405">
@@ -41872,7 +41872,7 @@
         </is>
       </c>
       <c r="B405" s="2" t="n">
-        <v>37.88009643554688</v>
+        <v>37.88008880615234</v>
       </c>
     </row>
     <row r="406">
@@ -41902,7 +41902,7 @@
         </is>
       </c>
       <c r="B408" s="2" t="n">
-        <v>39.03162384033203</v>
+        <v>39.0316276550293</v>
       </c>
     </row>
     <row r="409">
@@ -41912,7 +41912,7 @@
         </is>
       </c>
       <c r="B409" s="2" t="n">
-        <v>39.05949401855469</v>
+        <v>39.05949020385742</v>
       </c>
     </row>
     <row r="410">
@@ -41922,7 +41922,7 @@
         </is>
       </c>
       <c r="B410" s="2" t="n">
-        <v>39.09663391113281</v>
+        <v>39.09663772583008</v>
       </c>
     </row>
     <row r="411">
@@ -41932,7 +41932,7 @@
         </is>
       </c>
       <c r="B411" s="2" t="n">
-        <v>39.46809768676758</v>
+        <v>39.46810150146484</v>
       </c>
     </row>
     <row r="412">
@@ -41972,7 +41972,7 @@
         </is>
       </c>
       <c r="B415" s="2" t="n">
-        <v>38.88303756713867</v>
+        <v>38.8830451965332</v>
       </c>
     </row>
     <row r="416">
@@ -41982,7 +41982,7 @@
         </is>
       </c>
       <c r="B416" s="2" t="n">
-        <v>38.65087509155273</v>
+        <v>38.65087127685547</v>
       </c>
     </row>
     <row r="417">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="B417" s="2" t="n">
-        <v>37.96366500854492</v>
+        <v>37.96367263793945</v>
       </c>
     </row>
     <row r="418">
@@ -42022,7 +42022,7 @@
         </is>
       </c>
       <c r="B420" s="2" t="n">
-        <v>37.50862503051758</v>
+        <v>37.50862121582031</v>
       </c>
     </row>
     <row r="421">
@@ -42032,7 +42032,7 @@
         </is>
       </c>
       <c r="B421" s="2" t="n">
-        <v>37.68507385253906</v>
+        <v>37.6850700378418</v>
       </c>
     </row>
     <row r="422">
@@ -42052,7 +42052,7 @@
         </is>
       </c>
       <c r="B423" s="2" t="n">
-        <v>37.62935256958008</v>
+        <v>37.62934494018555</v>
       </c>
     </row>
     <row r="424">
@@ -42062,7 +42062,7 @@
         </is>
       </c>
       <c r="B424" s="2" t="n">
-        <v>37.5643424987793</v>
+        <v>37.56434631347656</v>
       </c>
     </row>
     <row r="425">
@@ -42072,7 +42072,7 @@
         </is>
       </c>
       <c r="B425" s="2" t="n">
-        <v>37.24860000610352</v>
+        <v>37.24860382080078</v>
       </c>
     </row>
     <row r="426">
@@ -42082,7 +42082,7 @@
         </is>
       </c>
       <c r="B426" s="2" t="n">
-        <v>37.25788497924805</v>
+        <v>37.25788879394531</v>
       </c>
     </row>
     <row r="427">
@@ -42092,7 +42092,7 @@
         </is>
       </c>
       <c r="B427" s="2" t="n">
-        <v>36.84927749633789</v>
+        <v>36.84927368164062</v>
       </c>
     </row>
     <row r="428">
@@ -42112,7 +42112,7 @@
         </is>
       </c>
       <c r="B429" s="2" t="n">
-        <v>36.20850372314453</v>
+        <v>36.20849609375</v>
       </c>
     </row>
     <row r="430">
@@ -42132,7 +42132,7 @@
         </is>
       </c>
       <c r="B431" s="2" t="n">
-        <v>35.56772613525391</v>
+        <v>35.56772232055664</v>
       </c>
     </row>
     <row r="432">
@@ -42142,7 +42142,7 @@
         </is>
       </c>
       <c r="B432" s="2" t="n">
-        <v>35.75345611572266</v>
+        <v>35.75345993041992</v>
       </c>
     </row>
     <row r="433">
@@ -42152,7 +42152,7 @@
         </is>
       </c>
       <c r="B433" s="2" t="n">
-        <v>35.50271987915039</v>
+        <v>35.50271606445312</v>
       </c>
     </row>
     <row r="434">
@@ -42162,7 +42162,7 @@
         </is>
       </c>
       <c r="B434" s="2" t="n">
-        <v>36.26421737670898</v>
+        <v>36.26422119140625</v>
       </c>
     </row>
     <row r="435">
@@ -42232,7 +42232,7 @@
         </is>
       </c>
       <c r="B441" s="2" t="n">
-        <v>35.14053726196289</v>
+        <v>35.14054107666016</v>
       </c>
     </row>
     <row r="442">
@@ -42252,7 +42252,7 @@
         </is>
       </c>
       <c r="B443" s="2" t="n">
-        <v>35.21482849121094</v>
+        <v>35.21483612060547</v>
       </c>
     </row>
     <row r="444">
@@ -42262,7 +42262,7 @@
         </is>
       </c>
       <c r="B444" s="2" t="n">
-        <v>34.61119842529297</v>
+        <v>34.61120223999023</v>
       </c>
     </row>
     <row r="445">
@@ -42272,7 +42272,7 @@
         </is>
       </c>
       <c r="B445" s="2" t="n">
-        <v>35.14053726196289</v>
+        <v>35.14054107666016</v>
       </c>
     </row>
     <row r="446">
@@ -42282,7 +42282,7 @@
         </is>
       </c>
       <c r="B446" s="2" t="n">
-        <v>34.92695236206055</v>
+        <v>34.92694854736328</v>
       </c>
     </row>
     <row r="447">
@@ -42312,7 +42312,7 @@
         </is>
       </c>
       <c r="B449" s="2" t="n">
-        <v>35.51200485229492</v>
+        <v>35.51200866699219</v>
       </c>
     </row>
     <row r="450">
@@ -42352,7 +42352,7 @@
         </is>
       </c>
       <c r="B453" s="2" t="n">
-        <v>36.22707366943359</v>
+        <v>36.22706985473633</v>
       </c>
     </row>
     <row r="454">
@@ -42382,7 +42382,7 @@
         </is>
       </c>
       <c r="B456" s="2" t="n">
-        <v>36.64496612548828</v>
+        <v>36.64496994018555</v>
       </c>
     </row>
     <row r="457">
@@ -42412,7 +42412,7 @@
         </is>
       </c>
       <c r="B459" s="2" t="n">
-        <v>36.43137359619141</v>
+        <v>36.43138122558594</v>
       </c>
     </row>
     <row r="460">
@@ -42422,7 +42422,7 @@
         </is>
       </c>
       <c r="B460" s="2" t="n">
-        <v>36.5799674987793</v>
+        <v>36.57996368408203</v>
       </c>
     </row>
     <row r="461">
@@ -42432,7 +42432,7 @@
         </is>
       </c>
       <c r="B461" s="2" t="n">
-        <v>36.61710739135742</v>
+        <v>36.61711502075195</v>
       </c>
     </row>
     <row r="462">
@@ -42452,7 +42452,7 @@
         </is>
       </c>
       <c r="B463" s="2" t="n">
-        <v>36.5799674987793</v>
+        <v>36.57996368408203</v>
       </c>
     </row>
     <row r="464">
@@ -42502,7 +42502,7 @@
         </is>
       </c>
       <c r="B468" s="2" t="n">
-        <v>36.62639236450195</v>
+        <v>36.62639617919922</v>
       </c>
     </row>
     <row r="469">
@@ -42512,7 +42512,7 @@
         </is>
       </c>
       <c r="B469" s="2" t="n">
-        <v>36.5706787109375</v>
+        <v>36.57068252563477</v>
       </c>
     </row>
     <row r="470">
@@ -42522,7 +42522,7 @@
         </is>
       </c>
       <c r="B470" s="2" t="n">
-        <v>36.22707366943359</v>
+        <v>36.22706985473633</v>
       </c>
     </row>
     <row r="471">
@@ -42542,7 +42542,7 @@
         </is>
       </c>
       <c r="B472" s="2" t="n">
-        <v>35.46556854248047</v>
+        <v>35.4655647277832</v>
       </c>
     </row>
     <row r="473">
@@ -42562,7 +42562,7 @@
         </is>
       </c>
       <c r="B474" s="2" t="n">
-        <v>36.15277862548828</v>
+        <v>36.15277481079102</v>
       </c>
     </row>
     <row r="475">
@@ -42582,7 +42582,7 @@
         </is>
       </c>
       <c r="B476" s="2" t="n">
-        <v>36.21778106689453</v>
+        <v>36.2177848815918</v>
       </c>
     </row>
     <row r="477">
@@ -42612,7 +42612,7 @@
         </is>
       </c>
       <c r="B479" s="2" t="n">
-        <v>36.0970573425293</v>
+        <v>36.09705352783203</v>
       </c>
     </row>
     <row r="480">
@@ -42622,7 +42622,7 @@
         </is>
       </c>
       <c r="B480" s="2" t="n">
-        <v>36.5799674987793</v>
+        <v>36.57996368408203</v>
       </c>
     </row>
     <row r="481">
@@ -42632,7 +42632,7 @@
         </is>
       </c>
       <c r="B481" s="2" t="n">
-        <v>36.59854125976562</v>
+        <v>36.59853363037109</v>
       </c>
     </row>
     <row r="482">
@@ -42642,7 +42642,7 @@
         </is>
       </c>
       <c r="B482" s="2" t="n">
-        <v>36.37565612792969</v>
+        <v>36.37565994262695</v>
       </c>
     </row>
     <row r="483">
@@ -42652,7 +42652,7 @@
         </is>
       </c>
       <c r="B483" s="2" t="n">
-        <v>36.35708999633789</v>
+        <v>36.35708618164062</v>
       </c>
     </row>
     <row r="484">
@@ -42662,7 +42662,7 @@
         </is>
       </c>
       <c r="B484" s="2" t="n">
-        <v>36.22707366943359</v>
+        <v>36.22706985473633</v>
       </c>
     </row>
     <row r="485">
@@ -42672,7 +42672,7 @@
         </is>
       </c>
       <c r="B485" s="2" t="n">
-        <v>35.79988861083984</v>
+        <v>35.79988479614258</v>
       </c>
     </row>
     <row r="486">
@@ -42682,7 +42682,7 @@
         </is>
       </c>
       <c r="B486" s="2" t="n">
-        <v>36.45923614501953</v>
+        <v>36.4592399597168</v>
       </c>
     </row>
     <row r="487">
@@ -42702,7 +42702,7 @@
         </is>
       </c>
       <c r="B488" s="2" t="n">
-        <v>36.36637496948242</v>
+        <v>36.36637115478516</v>
       </c>
     </row>
     <row r="489">
@@ -42712,7 +42712,7 @@
         </is>
       </c>
       <c r="B489" s="2" t="n">
-        <v>36.17135620117188</v>
+        <v>36.17135238647461</v>
       </c>
     </row>
     <row r="490">
@@ -42752,7 +42752,7 @@
         </is>
       </c>
       <c r="B493" s="2" t="n">
-        <v>35.66059494018555</v>
+        <v>35.66058731079102</v>
       </c>
     </row>
     <row r="494">
@@ -42772,7 +42772,7 @@
         </is>
       </c>
       <c r="B495" s="2" t="n">
-        <v>36.21778106689453</v>
+        <v>36.2177848815918</v>
       </c>
     </row>
     <row r="496">
@@ -42782,7 +42782,7 @@
         </is>
       </c>
       <c r="B496" s="2" t="n">
-        <v>35.79988861083984</v>
+        <v>35.79988479614258</v>
       </c>
     </row>
     <row r="497">
@@ -42792,7 +42792,7 @@
         </is>
       </c>
       <c r="B497" s="2" t="n">
-        <v>35.46556854248047</v>
+        <v>35.4655647277832</v>
       </c>
     </row>
     <row r="498">
@@ -42802,7 +42802,7 @@
         </is>
       </c>
       <c r="B498" s="2" t="n">
-        <v>36.0970573425293</v>
+        <v>36.09705352783203</v>
       </c>
     </row>
     <row r="499">
@@ -42832,7 +42832,7 @@
         </is>
       </c>
       <c r="B501" s="2" t="n">
-        <v>37.03501129150391</v>
+        <v>37.03500747680664</v>
       </c>
     </row>
     <row r="502">
@@ -42852,7 +42852,7 @@
         </is>
       </c>
       <c r="B503" s="2" t="n">
-        <v>37.13796615600586</v>
+        <v>37.13796234130859</v>
       </c>
     </row>
     <row r="504">
@@ -42872,7 +42872,7 @@
         </is>
       </c>
       <c r="B505" s="2" t="n">
-        <v>37.38130569458008</v>
+        <v>37.38130187988281</v>
       </c>
     </row>
     <row r="506">
@@ -42882,7 +42882,7 @@
         </is>
       </c>
       <c r="B506" s="2" t="n">
-        <v>37.75568389892578</v>
+        <v>37.75568008422852</v>
       </c>
     </row>
     <row r="507">
@@ -42902,7 +42902,7 @@
         </is>
       </c>
       <c r="B508" s="2" t="n">
-        <v>38.39211654663086</v>
+        <v>38.39211273193359</v>
       </c>
     </row>
     <row r="509">
@@ -42912,7 +42912,7 @@
         </is>
       </c>
       <c r="B509" s="2" t="n">
-        <v>38.26108551025391</v>
+        <v>38.26108932495117</v>
       </c>
     </row>
     <row r="510">
@@ -42942,7 +42942,7 @@
         </is>
       </c>
       <c r="B512" s="2" t="n">
-        <v>37.2034797668457</v>
+        <v>37.20347595214844</v>
       </c>
     </row>
     <row r="513">
@@ -42952,7 +42952,7 @@
         </is>
       </c>
       <c r="B513" s="2" t="n">
-        <v>36.66062927246094</v>
+        <v>36.6606330871582</v>
       </c>
     </row>
     <row r="514">
@@ -42962,7 +42962,7 @@
         </is>
       </c>
       <c r="B514" s="2" t="n">
-        <v>36.78230285644531</v>
+        <v>36.78230667114258</v>
       </c>
     </row>
     <row r="515">
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="B515" s="2" t="n">
-        <v>37.15667724609375</v>
+        <v>37.15668487548828</v>
       </c>
     </row>
     <row r="516">
@@ -42982,7 +42982,7 @@
         </is>
       </c>
       <c r="B516" s="2" t="n">
-        <v>36.93205642700195</v>
+        <v>36.93206024169922</v>
       </c>
     </row>
     <row r="517">
@@ -42992,7 +42992,7 @@
         </is>
       </c>
       <c r="B517" s="2" t="n">
-        <v>36.73550796508789</v>
+        <v>36.73550415039062</v>
       </c>
     </row>
     <row r="518">
@@ -43002,7 +43002,7 @@
         </is>
       </c>
       <c r="B518" s="2" t="n">
-        <v>37.0256462097168</v>
+        <v>37.02565002441406</v>
       </c>
     </row>
     <row r="519">
@@ -43012,7 +43012,7 @@
         </is>
       </c>
       <c r="B519" s="2" t="n">
-        <v>37.43746566772461</v>
+        <v>37.43745803833008</v>
       </c>
     </row>
     <row r="520">
@@ -43022,7 +43022,7 @@
         </is>
       </c>
       <c r="B520" s="2" t="n">
-        <v>37.21282958984375</v>
+        <v>37.21283340454102</v>
       </c>
     </row>
     <row r="521">
@@ -43052,7 +43052,7 @@
         </is>
       </c>
       <c r="B523" s="2" t="n">
-        <v>36.89461898803711</v>
+        <v>36.89461135864258</v>
       </c>
     </row>
     <row r="524">
@@ -43092,7 +43092,7 @@
         </is>
       </c>
       <c r="B527" s="2" t="n">
-        <v>38.38275146484375</v>
+        <v>38.38275527954102</v>
       </c>
     </row>
     <row r="528">
@@ -43122,7 +43122,7 @@
         </is>
       </c>
       <c r="B530" s="2" t="n">
-        <v>38.07389831542969</v>
+        <v>38.07390213012695</v>
       </c>
     </row>
     <row r="531">
@@ -43132,7 +43132,7 @@
         </is>
       </c>
       <c r="B531" s="2" t="n">
-        <v>37.79311370849609</v>
+        <v>37.79311752319336</v>
       </c>
     </row>
     <row r="532">
@@ -43172,7 +43172,7 @@
         </is>
       </c>
       <c r="B535" s="2" t="n">
-        <v>38.7945671081543</v>
+        <v>38.79457092285156</v>
       </c>
     </row>
     <row r="536">
@@ -43192,7 +43192,7 @@
         </is>
       </c>
       <c r="B537" s="2" t="n">
-        <v>39.24381637573242</v>
+        <v>39.24382019042969</v>
       </c>
     </row>
     <row r="538">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="B539" s="2" t="n">
-        <v>38.7664909362793</v>
+        <v>38.76648712158203</v>
       </c>
     </row>
     <row r="540">
@@ -43232,7 +43232,7 @@
         </is>
       </c>
       <c r="B541" s="2" t="n">
-        <v>37.98966217041016</v>
+        <v>37.98966598510742</v>
       </c>
     </row>
     <row r="542">
@@ -43242,7 +43242,7 @@
         </is>
       </c>
       <c r="B542" s="2" t="n">
-        <v>37.94287109375</v>
+        <v>37.94286727905273</v>
       </c>
     </row>
     <row r="543">
@@ -43282,7 +43282,7 @@
         </is>
       </c>
       <c r="B546" s="2" t="n">
-        <v>37.57785034179688</v>
+        <v>37.57785415649414</v>
       </c>
     </row>
     <row r="547">
@@ -43292,7 +43292,7 @@
         </is>
       </c>
       <c r="B547" s="2" t="n">
-        <v>37.0256462097168</v>
+        <v>37.02565002441406</v>
       </c>
     </row>
     <row r="548">
@@ -43342,7 +43342,7 @@
         </is>
       </c>
       <c r="B552" s="2" t="n">
-        <v>35.93996429443359</v>
+        <v>35.93996047973633</v>
       </c>
     </row>
     <row r="553">
@@ -43352,7 +43352,7 @@
         </is>
       </c>
       <c r="B553" s="2" t="n">
-        <v>36.02420043945312</v>
+        <v>36.02419662475586</v>
       </c>
     </row>
     <row r="554">
@@ -43382,7 +43382,7 @@
         </is>
       </c>
       <c r="B556" s="2" t="n">
-        <v>36.37985229492188</v>
+        <v>36.37984848022461</v>
       </c>
     </row>
     <row r="557">
@@ -43392,7 +43392,7 @@
         </is>
       </c>
       <c r="B557" s="2" t="n">
-        <v>36.41728591918945</v>
+        <v>36.41728973388672</v>
       </c>
     </row>
     <row r="558">
@@ -43412,7 +43412,7 @@
         </is>
       </c>
       <c r="B559" s="2" t="n">
-        <v>37.24091720581055</v>
+        <v>37.24091339111328</v>
       </c>
     </row>
     <row r="560">
@@ -43432,7 +43432,7 @@
         </is>
       </c>
       <c r="B561" s="2" t="n">
-        <v>36.66062927246094</v>
+        <v>36.6606330871582</v>
       </c>
     </row>
     <row r="562">
@@ -43442,7 +43442,7 @@
         </is>
       </c>
       <c r="B562" s="2" t="n">
-        <v>37.09116744995117</v>
+        <v>37.09117126464844</v>
       </c>
     </row>
     <row r="563">
@@ -43462,7 +43462,7 @@
         </is>
       </c>
       <c r="B564" s="2" t="n">
-        <v>36.58576202392578</v>
+        <v>36.58575820922852</v>
       </c>
     </row>
     <row r="565">
@@ -43482,7 +43482,7 @@
         </is>
       </c>
       <c r="B566" s="2" t="n">
-        <v>36.23009872436523</v>
+        <v>36.2301025390625</v>
       </c>
     </row>
     <row r="567">
@@ -43522,7 +43522,7 @@
         </is>
       </c>
       <c r="B570" s="2" t="n">
-        <v>36.76358795166016</v>
+        <v>36.76358413696289</v>
       </c>
     </row>
     <row r="571">
@@ -43552,7 +43552,7 @@
         </is>
       </c>
       <c r="B573" s="2" t="n">
-        <v>36.36112976074219</v>
+        <v>36.36113739013672</v>
       </c>
     </row>
     <row r="574">
@@ -43582,7 +43582,7 @@
         </is>
       </c>
       <c r="B576" s="2" t="n">
-        <v>36.0054817199707</v>
+        <v>36.00548553466797</v>
       </c>
     </row>
     <row r="577">
@@ -43592,7 +43592,7 @@
         </is>
       </c>
       <c r="B577" s="2" t="n">
-        <v>35.84637451171875</v>
+        <v>35.84637069702148</v>
       </c>
     </row>
     <row r="578">
@@ -43602,7 +43602,7 @@
         </is>
       </c>
       <c r="B578" s="2" t="n">
-        <v>35.34096527099609</v>
+        <v>35.34096145629883</v>
       </c>
     </row>
     <row r="579">
@@ -43612,7 +43612,7 @@
         </is>
       </c>
       <c r="B579" s="2" t="n">
-        <v>35.39712142944336</v>
+        <v>35.39711761474609</v>
       </c>
     </row>
     <row r="580">
@@ -43622,7 +43622,7 @@
         </is>
       </c>
       <c r="B580" s="2" t="n">
-        <v>35.49070739746094</v>
+        <v>35.4907112121582</v>
       </c>
     </row>
     <row r="581">
@@ -43642,7 +43642,7 @@
         </is>
       </c>
       <c r="B582" s="2" t="n">
-        <v>35.34096527099609</v>
+        <v>35.34096145629883</v>
       </c>
     </row>
     <row r="583">
@@ -43652,7 +43652,7 @@
         </is>
       </c>
       <c r="B583" s="2" t="n">
-        <v>34.87299346923828</v>
+        <v>34.87299728393555</v>
       </c>
     </row>
     <row r="584">
@@ -43682,7 +43682,7 @@
         </is>
       </c>
       <c r="B586" s="2" t="n">
-        <v>35.4064826965332</v>
+        <v>35.40648651123047</v>
       </c>
     </row>
     <row r="587">
@@ -43702,7 +43702,7 @@
         </is>
       </c>
       <c r="B588" s="2" t="n">
-        <v>35.74341583251953</v>
+        <v>35.74341201782227</v>
       </c>
     </row>
     <row r="589">
@@ -43732,7 +43732,7 @@
         </is>
       </c>
       <c r="B591" s="2" t="n">
-        <v>35.43455505371094</v>
+        <v>35.43456268310547</v>
       </c>
     </row>
     <row r="592">
@@ -43742,7 +43742,7 @@
         </is>
       </c>
       <c r="B592" s="2" t="n">
-        <v>35.69662094116211</v>
+        <v>35.69661712646484</v>
       </c>
     </row>
     <row r="593">
@@ -43772,7 +43772,7 @@
         </is>
       </c>
       <c r="B595" s="2" t="n">
-        <v>34.85427856445312</v>
+        <v>34.85427474975586</v>
       </c>
     </row>
     <row r="596">
@@ -43782,7 +43782,7 @@
         </is>
       </c>
       <c r="B596" s="2" t="n">
-        <v>34.43310165405273</v>
+        <v>34.43310546875</v>
       </c>
     </row>
     <row r="597">
@@ -43832,7 +43832,7 @@
         </is>
       </c>
       <c r="B601" s="2" t="n">
-        <v>34.18975448608398</v>
+        <v>34.18976211547852</v>
       </c>
     </row>
     <row r="602">
@@ -43852,7 +43852,7 @@
         </is>
       </c>
       <c r="B603" s="2" t="n">
-        <v>34.34886932373047</v>
+        <v>34.34887313842773</v>
       </c>
     </row>
     <row r="604">
@@ -43872,7 +43872,7 @@
         </is>
       </c>
       <c r="B605" s="2" t="n">
-        <v>35.27544403076172</v>
+        <v>35.27544784545898</v>
       </c>
     </row>
     <row r="606">
@@ -43902,7 +43902,7 @@
         </is>
       </c>
       <c r="B608" s="2" t="n">
-        <v>36.22074127197266</v>
+        <v>36.22074508666992</v>
       </c>
     </row>
     <row r="609">
@@ -43912,7 +43912,7 @@
         </is>
       </c>
       <c r="B609" s="2" t="n">
-        <v>35.97739791870117</v>
+        <v>35.9774055480957</v>
       </c>
     </row>
     <row r="610">
@@ -43932,7 +43932,7 @@
         </is>
       </c>
       <c r="B611" s="2" t="n">
-        <v>35.89316558837891</v>
+        <v>35.89316177368164</v>
       </c>
     </row>
     <row r="612">
@@ -43942,7 +43942,7 @@
         </is>
       </c>
       <c r="B612" s="2" t="n">
-        <v>35.88380432128906</v>
+        <v>35.88380813598633</v>
       </c>
     </row>
     <row r="613">
@@ -43952,7 +43952,7 @@
         </is>
       </c>
       <c r="B613" s="2" t="n">
-        <v>36.83845901489258</v>
+        <v>36.83846282958984</v>
       </c>
     </row>
     <row r="614">
@@ -43962,7 +43962,7 @@
         </is>
       </c>
       <c r="B614" s="2" t="n">
-        <v>37.14731597900391</v>
+        <v>37.14731979370117</v>
       </c>
     </row>
     <row r="615">
@@ -43982,7 +43982,7 @@
         </is>
       </c>
       <c r="B616" s="2" t="n">
-        <v>36.83845901489258</v>
+        <v>36.83846282958984</v>
       </c>
     </row>
     <row r="617">
@@ -44002,7 +44002,7 @@
         </is>
       </c>
       <c r="B618" s="2" t="n">
-        <v>37.06308364868164</v>
+        <v>37.06307983398438</v>
       </c>
     </row>
     <row r="619">
@@ -44012,7 +44012,7 @@
         </is>
       </c>
       <c r="B619" s="2" t="n">
-        <v>36.98821640014648</v>
+        <v>36.98821258544922</v>
       </c>
     </row>
     <row r="620">
@@ -44062,7 +44062,7 @@
         </is>
       </c>
       <c r="B624" s="2" t="n">
-        <v>37.0256462097168</v>
+        <v>37.02565002441406</v>
       </c>
     </row>
     <row r="625">
@@ -44082,7 +44082,7 @@
         </is>
       </c>
       <c r="B626" s="2" t="n">
-        <v>36.76358795166016</v>
+        <v>36.76358413696289</v>
       </c>
     </row>
     <row r="627">
@@ -44102,7 +44102,7 @@
         </is>
       </c>
       <c r="B628" s="2" t="n">
-        <v>36.49216842651367</v>
+        <v>36.49216461181641</v>
       </c>
     </row>
     <row r="629">
@@ -44112,7 +44112,7 @@
         </is>
       </c>
       <c r="B629" s="2" t="n">
-        <v>36.66999435424805</v>
+        <v>36.66999053955078</v>
       </c>
     </row>
     <row r="630">
@@ -44122,7 +44122,7 @@
         </is>
       </c>
       <c r="B630" s="2" t="n">
-        <v>36.51088333129883</v>
+        <v>36.51087951660156</v>
       </c>
     </row>
     <row r="631">
@@ -44142,7 +44142,7 @@
         </is>
       </c>
       <c r="B632" s="2" t="n">
-        <v>36.73550796508789</v>
+        <v>36.73550415039062</v>
       </c>
     </row>
     <row r="633">
@@ -44152,7 +44152,7 @@
         </is>
       </c>
       <c r="B633" s="2" t="n">
-        <v>37.10052108764648</v>
+        <v>37.10052871704102</v>
       </c>
     </row>
     <row r="634">
@@ -44162,7 +44162,7 @@
         </is>
       </c>
       <c r="B634" s="2" t="n">
-        <v>37.64336395263672</v>
+        <v>37.64336776733398</v>
       </c>
     </row>
     <row r="635">
@@ -44182,7 +44182,7 @@
         </is>
       </c>
       <c r="B636" s="2" t="n">
-        <v>37.40002059936523</v>
+        <v>37.4000244140625</v>
       </c>
     </row>
     <row r="637">
@@ -44192,7 +44192,7 @@
         </is>
       </c>
       <c r="B637" s="2" t="n">
-        <v>37.71824264526367</v>
+        <v>37.71824645996094</v>
       </c>
     </row>
     <row r="638">
@@ -44212,7 +44212,7 @@
         </is>
       </c>
       <c r="B639" s="2" t="n">
-        <v>37.73540496826172</v>
+        <v>37.73540878295898</v>
       </c>
     </row>
     <row r="640">
@@ -44242,7 +44242,7 @@
         </is>
       </c>
       <c r="B642" s="2" t="n">
-        <v>38.06917953491211</v>
+        <v>38.06917572021484</v>
       </c>
     </row>
     <row r="643">
@@ -44252,7 +44252,7 @@
         </is>
       </c>
       <c r="B643" s="2" t="n">
-        <v>38.36480712890625</v>
+        <v>38.36480331420898</v>
       </c>
     </row>
     <row r="644">
@@ -44272,7 +44272,7 @@
         </is>
       </c>
       <c r="B645" s="2" t="n">
-        <v>37.89752960205078</v>
+        <v>37.89752578735352</v>
       </c>
     </row>
     <row r="646">
@@ -44302,7 +44302,7 @@
         </is>
       </c>
       <c r="B648" s="2" t="n">
-        <v>37.61143493652344</v>
+        <v>37.61143112182617</v>
       </c>
     </row>
     <row r="649">
@@ -44322,7 +44322,7 @@
         </is>
       </c>
       <c r="B650" s="2" t="n">
-        <v>37.18230056762695</v>
+        <v>37.18229675292969</v>
       </c>
     </row>
     <row r="651">
@@ -44382,7 +44382,7 @@
         </is>
       </c>
       <c r="B656" s="2" t="n">
-        <v>36.22866439819336</v>
+        <v>36.22866058349609</v>
       </c>
     </row>
     <row r="657">
@@ -44392,7 +44392,7 @@
         </is>
       </c>
       <c r="B657" s="2" t="n">
-        <v>36.61011505126953</v>
+        <v>36.61011123657227</v>
       </c>
     </row>
     <row r="658">
@@ -44462,7 +44462,7 @@
         </is>
       </c>
       <c r="B664" s="2" t="n">
-        <v>36.81037521362305</v>
+        <v>36.81037902832031</v>
       </c>
     </row>
     <row r="665">
@@ -44472,7 +44472,7 @@
         </is>
       </c>
       <c r="B665" s="2" t="n">
-        <v>36.61011505126953</v>
+        <v>36.61011123657227</v>
       </c>
     </row>
     <row r="666">
@@ -44502,7 +44502,7 @@
         </is>
       </c>
       <c r="B668" s="2" t="n">
-        <v>36.90573883056641</v>
+        <v>36.90574264526367</v>
       </c>
     </row>
     <row r="669">
@@ -44622,7 +44622,7 @@
         </is>
       </c>
       <c r="B680" s="2" t="n">
-        <v>38.73672103881836</v>
+        <v>38.73672485351562</v>
       </c>
     </row>
     <row r="681">
@@ -44662,7 +44662,7 @@
         </is>
       </c>
       <c r="B684" s="2" t="n">
-        <v>38.11685943603516</v>
+        <v>38.11686325073242</v>
       </c>
     </row>
     <row r="685">
@@ -44682,7 +44682,7 @@
         </is>
       </c>
       <c r="B686" s="2" t="n">
-        <v>38.60321426391602</v>
+        <v>38.60321807861328</v>
       </c>
     </row>
     <row r="687">
@@ -44712,7 +44712,7 @@
         </is>
       </c>
       <c r="B689" s="2" t="n">
-        <v>38.72719192504883</v>
+        <v>38.72718811035156</v>
       </c>
     </row>
     <row r="690">
@@ -44722,7 +44722,7 @@
         </is>
       </c>
       <c r="B690" s="2" t="n">
-        <v>38.96559906005859</v>
+        <v>38.96560287475586</v>
       </c>
     </row>
     <row r="691">
@@ -44772,7 +44772,7 @@
         </is>
       </c>
       <c r="B695" s="2" t="n">
-        <v>39.11817932128906</v>
+        <v>39.11818313598633</v>
       </c>
     </row>
     <row r="696">
@@ -44782,7 +44782,7 @@
         </is>
       </c>
       <c r="B696" s="2" t="n">
-        <v>38.8797721862793</v>
+        <v>38.87976837158203</v>
       </c>
     </row>
     <row r="697">
@@ -44792,7 +44792,7 @@
         </is>
       </c>
       <c r="B697" s="2" t="n">
-        <v>38.9465217590332</v>
+        <v>38.94652557373047</v>
       </c>
     </row>
     <row r="698">
@@ -44812,7 +44812,7 @@
         </is>
       </c>
       <c r="B699" s="2" t="n">
-        <v>39.19447326660156</v>
+        <v>39.1944694519043</v>
       </c>
     </row>
     <row r="700">
@@ -44822,7 +44822,7 @@
         </is>
       </c>
       <c r="B700" s="2" t="n">
-        <v>39.24215316772461</v>
+        <v>39.24214935302734</v>
       </c>
     </row>
     <row r="701">
@@ -44832,7 +44832,7 @@
         </is>
       </c>
       <c r="B701" s="2" t="n">
-        <v>38.96559906005859</v>
+        <v>38.96560287475586</v>
       </c>
     </row>
     <row r="702">
@@ -44852,7 +44852,7 @@
         </is>
       </c>
       <c r="B703" s="2" t="n">
-        <v>38.96559906005859</v>
+        <v>38.96560287475586</v>
       </c>
     </row>
     <row r="704">
@@ -44882,7 +44882,7 @@
         </is>
       </c>
       <c r="B706" s="2" t="n">
-        <v>39.24215316772461</v>
+        <v>39.24214935302734</v>
       </c>
     </row>
     <row r="707">
@@ -44892,7 +44892,7 @@
         </is>
       </c>
       <c r="B707" s="2" t="n">
-        <v>39.36612701416016</v>
+        <v>39.36612319946289</v>
       </c>
     </row>
     <row r="708">
@@ -44902,7 +44902,7 @@
         </is>
       </c>
       <c r="B708" s="2" t="n">
-        <v>39.39473342895508</v>
+        <v>39.39473724365234</v>
       </c>
     </row>
     <row r="709">
@@ -44992,7 +44992,7 @@
         </is>
       </c>
       <c r="B717" s="2" t="n">
-        <v>37.89752960205078</v>
+        <v>37.89752578735352</v>
       </c>
     </row>
     <row r="718">
@@ -45052,7 +45052,7 @@
         </is>
       </c>
       <c r="B723" s="2" t="n">
-        <v>38.72719192504883</v>
+        <v>38.72718811035156</v>
       </c>
     </row>
     <row r="724">
@@ -45072,7 +45072,7 @@
         </is>
       </c>
       <c r="B725" s="2" t="n">
-        <v>39.26122665405273</v>
+        <v>39.26122283935547</v>
       </c>
     </row>
     <row r="726">
@@ -45092,7 +45092,7 @@
         </is>
       </c>
       <c r="B727" s="2" t="n">
-        <v>39.08957290649414</v>
+        <v>39.08956909179688</v>
       </c>
     </row>
     <row r="728">
@@ -45142,7 +45142,7 @@
         </is>
       </c>
       <c r="B732" s="2" t="n">
-        <v>40.31022262573242</v>
+        <v>40.31022644042969</v>
       </c>
     </row>
     <row r="733">
@@ -45232,7 +45232,7 @@
         </is>
       </c>
       <c r="B741" s="2" t="n">
-        <v>41.60717010498047</v>
+        <v>41.60717391967773</v>
       </c>
     </row>
     <row r="742">
@@ -45272,7 +45272,7 @@
         </is>
       </c>
       <c r="B745" s="2" t="n">
-        <v>41.02545547485352</v>
+        <v>41.02545166015625</v>
       </c>
     </row>
     <row r="746">
@@ -45312,7 +45312,7 @@
         </is>
       </c>
       <c r="B749" s="2" t="n">
-        <v>39.85248184204102</v>
+        <v>39.85248565673828</v>
       </c>
     </row>
     <row r="750">
@@ -45332,7 +45332,7 @@
         </is>
       </c>
       <c r="B751" s="2" t="n">
-        <v>39.70943450927734</v>
+        <v>39.70943069458008</v>
       </c>
     </row>
     <row r="752">
@@ -45362,7 +45362,7 @@
         </is>
       </c>
       <c r="B754" s="2" t="n">
-        <v>40.09089279174805</v>
+        <v>40.09088897705078</v>
       </c>
     </row>
     <row r="755">
@@ -45402,7 +45402,7 @@
         </is>
       </c>
       <c r="B758" s="2" t="n">
-        <v>40.50214004516602</v>
+        <v>40.50213623046875</v>
       </c>
     </row>
     <row r="759">
@@ -45452,7 +45452,7 @@
         </is>
       </c>
       <c r="B763" s="2" t="n">
-        <v>40.97264099121094</v>
+        <v>40.9726448059082</v>
       </c>
     </row>
     <row r="764">
@@ -45462,7 +45462,7 @@
         </is>
       </c>
       <c r="B764" s="2" t="n">
-        <v>40.97264099121094</v>
+        <v>40.9726448059082</v>
       </c>
     </row>
     <row r="765">
@@ -45542,7 +45542,7 @@
         </is>
       </c>
       <c r="B772" s="2" t="n">
-        <v>41.89445877075195</v>
+        <v>41.89446258544922</v>
       </c>
     </row>
     <row r="773">
@@ -45592,7 +45592,7 @@
         </is>
       </c>
       <c r="B777" s="2" t="n">
-        <v>42.73944854736328</v>
+        <v>42.73945236206055</v>
       </c>
     </row>
     <row r="778">
@@ -45622,7 +45622,7 @@
         </is>
       </c>
       <c r="B780" s="2" t="n">
-        <v>41.83684539794922</v>
+        <v>41.83684921264648</v>
       </c>
     </row>
     <row r="781">
@@ -45632,7 +45632,7 @@
         </is>
       </c>
       <c r="B781" s="2" t="n">
-        <v>41.44315338134766</v>
+        <v>41.44315719604492</v>
       </c>
     </row>
     <row r="782">
@@ -45672,7 +45672,7 @@
         </is>
       </c>
       <c r="B785" s="2" t="n">
-        <v>40.42531967163086</v>
+        <v>40.42531585693359</v>
       </c>
     </row>
     <row r="786">
@@ -45692,7 +45692,7 @@
         </is>
       </c>
       <c r="B787" s="2" t="n">
-        <v>40.67497634887695</v>
+        <v>40.67498016357422</v>
       </c>
     </row>
     <row r="788">
@@ -45792,7 +45792,7 @@
         </is>
       </c>
       <c r="B797" s="2" t="n">
-        <v>40.38691711425781</v>
+        <v>40.38691329956055</v>
       </c>
     </row>
     <row r="798">
@@ -45812,7 +45812,7 @@
         </is>
       </c>
       <c r="B799" s="2" t="n">
-        <v>40.97264099121094</v>
+        <v>40.9726448059082</v>
       </c>
     </row>
     <row r="800">
@@ -45832,7 +45832,7 @@
         </is>
       </c>
       <c r="B801" s="2" t="n">
-        <v>41.20310211181641</v>
+        <v>41.20309829711914</v>
       </c>
     </row>
     <row r="802">
@@ -45942,7 +45942,7 @@
         </is>
       </c>
       <c r="B812" s="2" t="n">
-        <v>41.64480209350586</v>
+        <v>41.64479827880859</v>
       </c>
     </row>
     <row r="813">
@@ -45982,7 +45982,7 @@
         </is>
       </c>
       <c r="B816" s="2" t="n">
-        <v>40.11804580688477</v>
+        <v>40.11804962158203</v>
       </c>
     </row>
     <row r="817">
@@ -46002,7 +46002,7 @@
         </is>
       </c>
       <c r="B818" s="2" t="n">
-        <v>40.30049133300781</v>
+        <v>40.30049514770508</v>
       </c>
     </row>
     <row r="819">
@@ -46022,7 +46022,7 @@
         </is>
       </c>
       <c r="B820" s="2" t="n">
-        <v>40.93424224853516</v>
+        <v>40.93423843383789</v>
       </c>
     </row>
     <row r="821">
@@ -46032,7 +46032,7 @@
         </is>
       </c>
       <c r="B821" s="2" t="n">
-        <v>41.12628555297852</v>
+        <v>41.12628173828125</v>
       </c>
     </row>
     <row r="822">
@@ -46052,7 +46052,7 @@
         </is>
       </c>
       <c r="B823" s="2" t="n">
-        <v>41.3087272644043</v>
+        <v>41.30872344970703</v>
       </c>
     </row>
     <row r="824">
@@ -46092,7 +46092,7 @@
         </is>
       </c>
       <c r="B827" s="2" t="n">
-        <v>42.27854537963867</v>
+        <v>42.27854919433594</v>
       </c>
     </row>
     <row r="828">
@@ -46102,7 +46102,7 @@
         </is>
       </c>
       <c r="B828" s="2" t="n">
-        <v>43.71887969970703</v>
+        <v>43.71887588500977</v>
       </c>
     </row>
     <row r="829">
@@ -46182,7 +46182,7 @@
         </is>
       </c>
       <c r="B836" s="2" t="n">
-        <v>45.10160064697266</v>
+        <v>45.10159683227539</v>
       </c>
     </row>
     <row r="837">
@@ -46222,7 +46222,7 @@
         </is>
       </c>
       <c r="B840" s="2" t="n">
-        <v>44.1989860534668</v>
+        <v>44.19898986816406</v>
       </c>
     </row>
     <row r="841">
@@ -46312,7 +46312,7 @@
         </is>
       </c>
       <c r="B849" s="2" t="n">
-        <v>43.43081283569336</v>
+        <v>43.43080902099609</v>
       </c>
     </row>
     <row r="850">
@@ -46322,7 +46322,7 @@
         </is>
       </c>
       <c r="B850" s="2" t="n">
-        <v>43.36359786987305</v>
+        <v>43.36360168457031</v>
       </c>
     </row>
     <row r="851">
@@ -46342,7 +46342,7 @@
         </is>
       </c>
       <c r="B852" s="2" t="n">
-        <v>43.51723480224609</v>
+        <v>43.51723098754883</v>
       </c>
     </row>
     <row r="853">
@@ -46382,7 +46382,7 @@
         </is>
       </c>
       <c r="B856" s="2" t="n">
-        <v>42.72024917602539</v>
+        <v>42.72025299072266</v>
       </c>
     </row>
     <row r="857">
@@ -46422,7 +46422,7 @@
         </is>
       </c>
       <c r="B860" s="2" t="n">
-        <v>43.95893478393555</v>
+        <v>43.95893096923828</v>
       </c>
     </row>
     <row r="861">
@@ -46542,7 +46542,7 @@
         </is>
       </c>
       <c r="B872" s="2" t="n">
-        <v>41.58719253540039</v>
+        <v>41.58718872070312</v>
       </c>
     </row>
     <row r="873">
@@ -46552,7 +46552,7 @@
         </is>
       </c>
       <c r="B873" s="2" t="n">
-        <v>41.41434478759766</v>
+        <v>41.41434860229492</v>
       </c>
     </row>
     <row r="874">
@@ -46602,7 +46602,7 @@
         </is>
       </c>
       <c r="B878" s="2" t="n">
-        <v>41.89445877075195</v>
+        <v>41.89446258544922</v>
       </c>
     </row>
     <row r="879">
@@ -46632,7 +46632,7 @@
         </is>
       </c>
       <c r="B881" s="2" t="n">
-        <v>42.96990966796875</v>
+        <v>42.96990585327148</v>
       </c>
     </row>
     <row r="882">
@@ -46642,7 +46642,7 @@
         </is>
       </c>
       <c r="B882" s="2" t="n">
-        <v>42.27854537963867</v>
+        <v>42.27854919433594</v>
       </c>
     </row>
     <row r="883">
@@ -46672,7 +46672,7 @@
         </is>
       </c>
       <c r="B885" s="2" t="n">
-        <v>42.27854537963867</v>
+        <v>42.27854919433594</v>
       </c>
     </row>
     <row r="886">
